--- a/data-manipulation-scripts/sheets-cleanup/sheets/LAMPADA LED 03_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/LAMPADA LED 03_02.xlsx
@@ -28,49 +28,49 @@
     <t>602883759435</t>
   </si>
   <si>
-    <t xml:space="preserve"> LAMPADA  LED  2 LADOS 12-80V 007278</t>
+    <t xml:space="preserve"> LAMPADA   IRON  2 LADOS H4 12-80V 007278</t>
   </si>
   <si>
     <t>6977790431014</t>
   </si>
   <si>
-    <t>LAMPADA LED TALLION FAROL H4</t>
+    <t>LAMPADA  TALLION FAROL H4</t>
   </si>
   <si>
     <t>631430290947</t>
   </si>
   <si>
-    <t>LAMPADA LED IRON 20W 8-80V 351904</t>
+    <t>LAMPADA  IRON 20W 8-80V 351904</t>
   </si>
   <si>
     <t>7891799338879</t>
   </si>
   <si>
-    <t>LAMPADA LED WURTH 12V 30/ 30W</t>
+    <t>LAMPADA  WURTH 12V 30/ 30W</t>
   </si>
   <si>
     <t>7891799111373</t>
   </si>
   <si>
-    <t>LAMPADA LED WURTH 12V 55W</t>
+    <t>LAMPADA WURTH 12V 55W</t>
   </si>
   <si>
     <t>7891799338893</t>
   </si>
   <si>
-    <t>LAMPADA LED 12V 35/ 35W</t>
+    <t>LAMPADA WURTH 12V 35/ 35W</t>
   </si>
   <si>
     <t>8711500879080</t>
   </si>
   <si>
-    <t>LAMPADA LED PHILIPS 12V 35</t>
+    <t>LAMPADA  PHILIPS 12V 35</t>
   </si>
   <si>
     <t>7895099121605</t>
   </si>
   <si>
-    <t xml:space="preserve"> LAMPADA LED HALOGENA IRON BIZ100/ BIZ125 043069</t>
+    <t xml:space="preserve"> LAMPADA  HALOGENA IRON BIZ100/ BIZ125 043069</t>
   </si>
   <si>
     <t>7895099121599</t>
@@ -82,31 +82,31 @@
     <t>7895099122954</t>
   </si>
   <si>
-    <t>LAMPADA LED HALOGENA IRON 12V 35x35W BIZ100/ BIZ125 038663</t>
+    <t>LAMPADA  HALOGENA IRON 12V 35x35W BIZ100/ BIZ125 038663</t>
   </si>
   <si>
     <t>8727900377910</t>
   </si>
   <si>
-    <t>LAMPADA LED PHILIPS 12V 35/35W H4FITMOTOC1</t>
+    <t>LAMPADA PHILIPS 12V 35/35W H4  37791060</t>
   </si>
   <si>
     <t xml:space="preserve"> 8727900351859</t>
   </si>
   <si>
-    <t>LAMPADA LED PHILIPS 12V 35/35W  12153ESC1</t>
+    <t>LAMPADA M5 PHILIPS 12V 35/35W  35185960</t>
   </si>
   <si>
     <t>8711500773593</t>
   </si>
   <si>
-    <t>LAMPADA LED PHILIPS S2 12V 35/35W 12728C1</t>
+    <t>LAMPADA  PHILIPS S2 12V 35/35W 12728C1</t>
   </si>
   <si>
     <t>6974260728254</t>
   </si>
   <si>
-    <t>LAMPADA LED PHILIPS 12V 4W</t>
+    <t>LAMPADA  PHILIPS 12V 4W</t>
   </si>
   <si>
     <t>7891579315977</t>
@@ -418,7 +418,9 @@
       <c r="C2" s="2">
         <v>16.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -430,7 +432,9 @@
       <c r="C3" s="2">
         <v>6.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>45.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -442,7 +446,9 @@
       <c r="C4" s="2">
         <v>7.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -454,7 +460,9 @@
       <c r="C5" s="2">
         <v>3.0</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>26.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -466,7 +474,9 @@
       <c r="C6" s="2">
         <v>3.0</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>26.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -478,7 +488,9 @@
       <c r="C7" s="2">
         <v>3.0</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="2">
+        <v>26.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -490,7 +502,9 @@
       <c r="C8" s="2">
         <v>6.0</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -502,7 +516,9 @@
       <c r="C9" s="2">
         <v>9.0</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -514,7 +530,9 @@
       <c r="C10" s="2">
         <v>2.0</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -526,7 +544,9 @@
       <c r="C11" s="2">
         <v>3.0</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -538,7 +558,9 @@
       <c r="C12" s="2">
         <v>2.0</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
@@ -550,7 +572,9 @@
       <c r="C13" s="2">
         <v>4.0</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="2">
+        <v>28.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
@@ -562,7 +586,9 @@
       <c r="C14" s="2">
         <v>1.0</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
@@ -574,7 +600,9 @@
       <c r="C15" s="2">
         <v>1.0</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
@@ -586,7 +614,9 @@
       <c r="C16" s="2">
         <v>1.0</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="2">
+        <v>25.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
